--- a/artfynd/A 43587-2021 artfynd.xlsx
+++ b/artfynd/A 43587-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43587-2021 artfynd.xlsx
+++ b/artfynd/A 43587-2021 artfynd.xlsx
@@ -4713,10 +4713,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117441404</v>
+        <v>117441267</v>
       </c>
       <c r="B32" t="n">
-        <v>102732</v>
+        <v>102734</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4759,14 +4759,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Furuhäll (1), Öl</t>
+          <t>Furuhäll 2, Öl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>602979</v>
+        <v>602996</v>
       </c>
       <c r="R32" t="n">
-        <v>6304852</v>
+        <v>6304889</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Hö-Bor-0083</t>
+          <t>Hö-Bor-5755</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>180 plantor+ 70 hybrid plantor fördelat på två fastigheter</t>
+          <t>Hybrider i hagtornshäck</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4840,10 +4840,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117441267</v>
+        <v>117441404</v>
       </c>
       <c r="B33" t="n">
-        <v>102732</v>
+        <v>102734</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4886,14 +4886,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Furuhäll 2, Öl</t>
+          <t>Furuhäll (1), Öl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>602996</v>
+        <v>602979</v>
       </c>
       <c r="R33" t="n">
-        <v>6304889</v>
+        <v>6304852</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Hö-Bor-5755</t>
+          <t>Hö-Bor-0083</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Hybrider i hagtornshäck</t>
+          <t>180 plantor+ 70 hybrid plantor fördelat på två fastigheter</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4967,10 +4967,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117969859</v>
+        <v>117969985</v>
       </c>
       <c r="B34" t="n">
-        <v>58129</v>
+        <v>58130</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5008,7 +5008,11 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>trafikdödad</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -5046,22 +5050,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 43587-2021 artfynd.xlsx
+++ b/artfynd/A 43587-2021 artfynd.xlsx
@@ -5089,10 +5089,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118461916</v>
+        <v>118462367</v>
       </c>
       <c r="B35" t="n">
-        <v>56262</v>
+        <v>9367</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5105,16 +5105,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100088</v>
+        <v>101246</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -5180,27 +5180,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Krälande.</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5228,10 +5213,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118462367</v>
+        <v>118461916</v>
       </c>
       <c r="B36" t="n">
-        <v>9367</v>
+        <v>56262</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5244,16 +5229,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>101246</v>
+        <v>100088</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5273,7 +5258,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -5319,12 +5304,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Krälande.</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 43587-2021 artfynd.xlsx
+++ b/artfynd/A 43587-2021 artfynd.xlsx
@@ -5089,10 +5089,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118462367</v>
+        <v>118461916</v>
       </c>
       <c r="B35" t="n">
-        <v>9367</v>
+        <v>56262</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5105,16 +5105,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101246</v>
+        <v>100088</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -5180,12 +5180,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Krälande.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5213,10 +5228,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118461916</v>
+        <v>118462367</v>
       </c>
       <c r="B36" t="n">
-        <v>56262</v>
+        <v>9367</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5229,16 +5244,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100088</v>
+        <v>101246</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5258,7 +5273,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -5304,27 +5319,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Krälande.</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 43587-2021 artfynd.xlsx
+++ b/artfynd/A 43587-2021 artfynd.xlsx
@@ -5355,7 +5355,7 @@
         <v>119959940</v>
       </c>
       <c r="B37" t="n">
-        <v>56233</v>
+        <v>56243</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>

--- a/artfynd/A 43587-2021 artfynd.xlsx
+++ b/artfynd/A 43587-2021 artfynd.xlsx
@@ -4716,7 +4716,7 @@
         <v>117441267</v>
       </c>
       <c r="B32" t="n">
-        <v>102977</v>
+        <v>102987</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>117441404</v>
       </c>
       <c r="B33" t="n">
-        <v>102977</v>
+        <v>102987</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/artfynd/A 43587-2021 artfynd.xlsx
+++ b/artfynd/A 43587-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4713,63 +4713,72 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117441267</v>
+        <v>119959940</v>
       </c>
       <c r="B32" t="n">
-        <v>102987</v>
+        <v>56243</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1661</v>
+        <v>100053</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Silverviol</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Viola alba</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Besser</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Furuhäll 2, Öl</t>
+          <t>Predikstolen, Öl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>602996</v>
+        <v>603052</v>
       </c>
       <c r="R32" t="n">
-        <v>6304889</v>
+        <v>6304833</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4791,24 +4800,24 @@
           <t>Köping</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>Hö-Bor-5755</t>
-        </is>
-      </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>22:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Hybrider i hagtornshäck</t>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>22:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4817,669 +4826,21 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kornelia Samarzija</t>
+          <t>Johan Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kornelia Samarzija</t>
+          <t>Via Johan Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>117441404</v>
-      </c>
-      <c r="B33" t="n">
-        <v>102987</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>1661</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Silverviol</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Viola alba</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Besser</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Furuhäll (1), Öl</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>602979</v>
-      </c>
-      <c r="R33" t="n">
-        <v>6304852</v>
-      </c>
-      <c r="S33" t="n">
-        <v>10</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Borgholm</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Öland</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Köping</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>Hö-Bor-0083</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2024-04-06</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2024-04-06</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>180 plantor+ 70 hybrid plantor fördelat på två fastigheter</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Kornelia Samarzija</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Kornelia Samarzija</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>117969859</v>
-      </c>
-      <c r="B34" t="n">
-        <v>58132</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>100117</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Långbensgroda</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Rana dalmatina</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Bonaparte, 1840</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Kolstad 39:33, Öl</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>603177</v>
-      </c>
-      <c r="R34" t="n">
-        <v>6304796</v>
-      </c>
-      <c r="S34" t="n">
-        <v>123</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Borgholm</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Öland</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Köping</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2024-05-14</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>19:38</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2024-05-14</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>19:38</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Jan Tingnert</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Jan Tingnert</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>118462367</v>
-      </c>
-      <c r="B35" t="n">
-        <v>9367</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>101246</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Ekoxe</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Lucanus cervus</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Kolstad 39:33, Öl</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>603177</v>
-      </c>
-      <c r="R35" t="n">
-        <v>6304796</v>
-      </c>
-      <c r="S35" t="n">
-        <v>123</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Borgholm</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Öland</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Köping</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Jan Tingnert</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Jan Tingnert</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>118461916</v>
-      </c>
-      <c r="B36" t="n">
-        <v>56264</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>100088</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Vanlig snok</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Natrix natrix</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Kolstad 39:33, Öl</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>603177</v>
-      </c>
-      <c r="R36" t="n">
-        <v>6304796</v>
-      </c>
-      <c r="S36" t="n">
-        <v>123</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Borgholm</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Öland</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Köping</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2024-07-15</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2024-07-15</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Krälande.</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Jan Tingnert</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Jan Tingnert</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>119959940</v>
-      </c>
-      <c r="B37" t="n">
-        <v>56243</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>100053</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Igelkott</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Erinaceus europaeus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Predikstolen, Öl</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>603052</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6304833</v>
-      </c>
-      <c r="S37" t="n">
-        <v>50</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Borgholm</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Öland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Köping</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Johan Nilsson</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Via Johan Nilsson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
         <is>
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>

--- a/artfynd/A 43587-2021 artfynd.xlsx
+++ b/artfynd/A 43587-2021 artfynd.xlsx
@@ -3796,12 +3796,7 @@
         <v>99826221</v>
       </c>
       <c r="B25" t="n">
-        <v>101105</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
-        </is>
+        <v>103234</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3845,10 +3840,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>602995.9245456469</v>
+        <v>602996</v>
       </c>
       <c r="R25" t="n">
-        <v>6304888.952197785</v>
+        <v>6304889</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3883,19 +3878,9 @@
           <t>2022-04-11</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-04-11</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3935,12 +3920,7 @@
         <v>99826149</v>
       </c>
       <c r="B26" t="n">
-        <v>101105</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
-        </is>
+        <v>103234</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3984,10 +3964,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>602978.763949143</v>
+        <v>602979</v>
       </c>
       <c r="R26" t="n">
-        <v>6304851.902166231</v>
+        <v>6304852</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4022,19 +4002,9 @@
           <t>2022-04-11</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-04-11</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">

--- a/artfynd/A 43587-2021 artfynd.xlsx
+++ b/artfynd/A 43587-2021 artfynd.xlsx
@@ -3796,7 +3796,7 @@
         <v>99826221</v>
       </c>
       <c r="B25" t="n">
-        <v>103234</v>
+        <v>103237</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>99826149</v>
       </c>
       <c r="B26" t="n">
-        <v>103234</v>
+        <v>103237</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 43587-2021 artfynd.xlsx
+++ b/artfynd/A 43587-2021 artfynd.xlsx
@@ -3796,7 +3796,7 @@
         <v>99826221</v>
       </c>
       <c r="B25" t="n">
-        <v>103237</v>
+        <v>103266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>99826149</v>
       </c>
       <c r="B26" t="n">
-        <v>103237</v>
+        <v>103266</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 43587-2021 artfynd.xlsx
+++ b/artfynd/A 43587-2021 artfynd.xlsx
@@ -3796,7 +3796,7 @@
         <v>99826221</v>
       </c>
       <c r="B25" t="n">
-        <v>103266</v>
+        <v>103278</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>99826149</v>
       </c>
       <c r="B26" t="n">
-        <v>103266</v>
+        <v>103278</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 43587-2021 artfynd.xlsx
+++ b/artfynd/A 43587-2021 artfynd.xlsx
@@ -3796,7 +3796,7 @@
         <v>99826221</v>
       </c>
       <c r="B25" t="n">
-        <v>103278</v>
+        <v>103279</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>99826149</v>
       </c>
       <c r="B26" t="n">
-        <v>103278</v>
+        <v>103279</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 43587-2021 artfynd.xlsx
+++ b/artfynd/A 43587-2021 artfynd.xlsx
@@ -3796,7 +3796,7 @@
         <v>99826221</v>
       </c>
       <c r="B25" t="n">
-        <v>103279</v>
+        <v>103284</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>99826149</v>
       </c>
       <c r="B26" t="n">
-        <v>103279</v>
+        <v>103284</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 43587-2021 artfynd.xlsx
+++ b/artfynd/A 43587-2021 artfynd.xlsx
@@ -3796,7 +3796,7 @@
         <v>99826221</v>
       </c>
       <c r="B25" t="n">
-        <v>103284</v>
+        <v>103288</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>99826149</v>
       </c>
       <c r="B26" t="n">
-        <v>103284</v>
+        <v>103288</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 43587-2021 artfynd.xlsx
+++ b/artfynd/A 43587-2021 artfynd.xlsx
@@ -3796,7 +3796,7 @@
         <v>99826221</v>
       </c>
       <c r="B25" t="n">
-        <v>103288</v>
+        <v>103290</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>99826149</v>
       </c>
       <c r="B26" t="n">
-        <v>103288</v>
+        <v>103290</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 43587-2021 artfynd.xlsx
+++ b/artfynd/A 43587-2021 artfynd.xlsx
@@ -3796,7 +3796,7 @@
         <v>99826221</v>
       </c>
       <c r="B25" t="n">
-        <v>103290</v>
+        <v>103300</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>99826149</v>
       </c>
       <c r="B26" t="n">
-        <v>103290</v>
+        <v>103300</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 43587-2021 artfynd.xlsx
+++ b/artfynd/A 43587-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97488057</v>
+        <v>6768133</v>
       </c>
       <c r="B2" t="n">
-        <v>8294</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103665</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106540</v>
+        <v>1661</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Silverviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Viola alba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>Besser</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -736,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603156.1160179721</v>
+        <v>602974</v>
       </c>
       <c r="R2" t="n">
-        <v>6304901.113334148</v>
+        <v>6304873</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,27 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-06-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-04-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>trädfönster B4, på vad det ser ut som en död ask</t>
+          <t>2008-04-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,39 +768,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>ädellövskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Roger Mugerwa Pettersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Thomas Gunnarsson, Eva Bjelkendal, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97498949</v>
+        <v>6768138</v>
       </c>
       <c r="B3" t="n">
-        <v>57587</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103665</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,46 +801,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100141</v>
+        <v>1661</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Silverviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Viola alba</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>Besser</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kolstad 39:33, Öl</t>
+          <t>Furuhäll (1), Öl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603177.3517046175</v>
+        <v>602979</v>
       </c>
       <c r="R3" t="n">
-        <v>6304795.586559884</v>
+        <v>6304852</v>
       </c>
       <c r="S3" t="n">
-        <v>123</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -896,29 +862,19 @@
           <t>Köping</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Hö-Bor-0083</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-04-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rapporterad i efterhand, tidpunkt osäker.</t>
+          <t>2008-04-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,78 +883,69 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Tingnert</t>
+          <t>Öland- Floraväktarna</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Tingnert</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97488051</v>
+        <v>6768135</v>
       </c>
       <c r="B4" t="n">
-        <v>12472</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103665</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102289</v>
+        <v>1661</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vasstandad trädbasbagge</t>
+          <t>Silverviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lissodema denticolle</t>
+          <t>Viola alba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1813)</t>
+          <t>Besser</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1007,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603034.2752251355</v>
+        <v>602993</v>
       </c>
       <c r="R4" t="n">
-        <v>6304777.834185833</v>
+        <v>6304865</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1037,27 +984,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-06-14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-04-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>trädfönster A2, på vad ser ut som en död ask</t>
+          <t>2008-04-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1066,39 +998,32 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>ädellövskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Roger Mugerwa Pettersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Thomas Gunnarsson, Eva Bjelkendal, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97498902</v>
+        <v>95668336</v>
       </c>
       <c r="B5" t="n">
-        <v>57150</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,46 +1031,49 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208260</v>
+        <v>1661</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Silverviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Viola alba</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Besser</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kolstad 39:33, Öl</t>
+          <t>Furuhäll, Öl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603177.3517046175</v>
+        <v>602996</v>
       </c>
       <c r="R5" t="n">
-        <v>6304795.586559884</v>
+        <v>6304889</v>
       </c>
       <c r="S5" t="n">
-        <v>123</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1169,27 +1097,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rapporterad i efterhand, tidpunkt osäker.</t>
+          <t>2021-04-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1202,30 +1115,30 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>i en hagtornshäck mot vägkant och gräsmatta</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan Tingnert</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Tingnert</t>
+          <t>Sten Linder-Aronson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97498905</v>
+        <v>95668346</v>
       </c>
       <c r="B6" t="n">
-        <v>57140</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,46 +1146,49 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100088</v>
+        <v>1661</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Silverviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Viola alba</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Besser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kolstad 39:33, Öl</t>
+          <t>Furuhäll Östra Bergklintsvägen 30, Öl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603177.3517046175</v>
+        <v>603139</v>
       </c>
       <c r="R6" t="n">
-        <v>6304795.586559884</v>
+        <v>6304735</v>
       </c>
       <c r="S6" t="n">
-        <v>123</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1296,27 +1212,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rapporterad i efterhand, tidpunkt osäker.</t>
+          <t>2021-04-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1329,84 +1230,76 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>i kanten av lövridå mot gräsmatta och väg</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Tingnert</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Tingnert</t>
+          <t>Sten Linder-Aronson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97488103</v>
+        <v>97498807</v>
       </c>
       <c r="B7" t="n">
-        <v>10568</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100782</v>
+        <v>1661</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Silverviol</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cypha apicalis</t>
+          <t>Viola alba</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brisout de Barneville, 1863)</t>
+          <t>Besser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Furuhäll, Öl</t>
+          <t>Kolstad 39:33, Öl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603156.1160179721</v>
+        <v>603177</v>
       </c>
       <c r="R7" t="n">
-        <v>6304901.113334148</v>
+        <v>6304796</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1430,27 +1323,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-06-14</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>trädfönster B4, på vad ser ut som en död ask</t>
+          <t>Rapporterad i efterhand, tidpunkt osäker.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1463,94 +1346,83 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>ädellövskog</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>Roger Mugerwa Pettersson</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Roger Mugerwa Pettersson</t>
+          <t>Jan Tingnert</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Jan Tingnert</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97488047</v>
+        <v>106536624</v>
       </c>
       <c r="B8" t="n">
-        <v>4696</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103666</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101929</v>
+        <v>1661</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Silverviol</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Trinodes hirtus</t>
+          <t>Viola alba</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fabricius, 1781)</t>
+          <t>Besser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>fönsterfälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Furuhäll, Öl</t>
+          <t>Häck, Borgholm, Öl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603156.1160179721</v>
+        <v>603010</v>
       </c>
       <c r="R8" t="n">
-        <v>6304901.113334148</v>
+        <v>6304877</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1574,27 +1446,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-06-14</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-08</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>trädfönster B4, på vad ser ut som en död ask</t>
+          <t>WSP Sverige AB</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1607,89 +1469,63 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>ädellövskog</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Roger Mugerwa Pettersson</t>
+          <t>Simon Selberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Simon Selberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97488044</v>
+        <v>559779</v>
       </c>
       <c r="B9" t="n">
-        <v>4696</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105392</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101929</v>
+        <v>1725</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spädnarv</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Trinodes hirtus</t>
+          <t>Arenaria leptoclados</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fabricius, 1781)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
+          <t>(Rchb.) Guss.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Furuhäll, Öl</t>
+          <t>St Elofs källa 450 m syd, Öl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603034.2752251355</v>
+        <v>603109</v>
       </c>
       <c r="R9" t="n">
-        <v>6304777.834185833</v>
+        <v>6304691</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1713,27 +1549,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-06-14</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1992-11-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1992-11-16</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>trädfönster A2, på vad ser ut som en död ask</t>
+          <t>Leg. Gunhild  Sven Johansson</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1742,24 +1568,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>ädellövskog</t>
-        </is>
-      </c>
+          <t>öppen jord på sommarstugtomt</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>Oskarshamn-Herbarium OHN</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Roger Mugerwa Pettersson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Via Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1769,12 +1600,7 @@
         <v>97498759</v>
       </c>
       <c r="B10" t="n">
-        <v>57133</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603177.3517046175</v>
+        <v>603177</v>
       </c>
       <c r="R10" t="n">
-        <v>6304795.586559884</v>
+        <v>6304796</v>
       </c>
       <c r="S10" t="n">
         <v>123</v>
@@ -1848,19 +1674,9 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-08-31</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1893,74 +1709,56 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97488071</v>
+        <v>97498886</v>
       </c>
       <c r="B11" t="n">
-        <v>12582</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100713</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tvåfärgad barksvartbagge</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corticeus bicolor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Olivier, 1790)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Furuhäll, Öl</t>
+          <t>Kolstad 39:33, Öl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603044.2056244101</v>
+        <v>603177</v>
       </c>
       <c r="R11" t="n">
-        <v>6304885.77222786</v>
+        <v>6304796</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1984,27 +1782,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-06-14</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>trädfönster B1, på vad ser ut som en död ask</t>
+          <t>Rapporterad i efterhand, tidpunkt osäker.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2013,39 +1801,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>ädellövskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Roger Mugerwa Pettersson</t>
+          <t>Jan Tingnert</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Jan Tingnert</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97488069</v>
+        <v>119959940</v>
       </c>
       <c r="B12" t="n">
-        <v>7082</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56845</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2053,21 +1830,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101784</v>
+        <v>100053</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Entandad plattbagge</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Silvanus unidentatus</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Olivier, 1790)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2075,36 +1852,34 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>fönsterfälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Furuhäll, Öl</t>
+          <t>Predikstolen, Öl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603068.0020412052</v>
+        <v>603052</v>
       </c>
       <c r="R12" t="n">
-        <v>6304920.253093851</v>
+        <v>6304833</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2128,27 +1903,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-06-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>trädfönster B2, på vad ser ut som en död ask</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2157,44 +1927,32 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>ädellövskog</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>Roger Mugerwa Pettersson</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Roger Mugerwa Pettersson</t>
+          <t>Johan Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Via Johan Nilsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97498698</v>
+        <v>97498905</v>
       </c>
       <c r="B13" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56895</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2202,21 +1960,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>100088</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2227,6 +1985,7 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2234,10 +1993,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603177.3517046175</v>
+        <v>603177</v>
       </c>
       <c r="R13" t="n">
-        <v>6304795.586559884</v>
+        <v>6304796</v>
       </c>
       <c r="S13" t="n">
         <v>123</v>
@@ -2264,22 +2023,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2312,44 +2061,40 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97498886</v>
+        <v>97498730</v>
       </c>
       <c r="B14" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58816</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100117</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rana dalmatina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Bonaparte, 1840</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
@@ -2360,10 +2105,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603177.3517046175</v>
+        <v>603177</v>
       </c>
       <c r="R14" t="n">
-        <v>6304795.586559884</v>
+        <v>6304796</v>
       </c>
       <c r="S14" t="n">
         <v>123</v>
@@ -2390,12 +2135,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2403,11 +2143,6 @@
           <t>2021-08-31</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>Rapporterad i efterhand, tidpunkt osäker.</t>
@@ -2419,6 +2154,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2437,15 +2173,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>97498679</v>
+        <v>97498949</v>
       </c>
       <c r="B15" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2453,31 +2184,32 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221141</v>
+        <v>100141</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2485,10 +2217,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603177.3517046175</v>
+        <v>603177</v>
       </c>
       <c r="R15" t="n">
-        <v>6304795.586559884</v>
+        <v>6304796</v>
       </c>
       <c r="S15" t="n">
         <v>123</v>
@@ -2518,19 +2250,9 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2563,15 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>97488075</v>
+        <v>97488071</v>
       </c>
       <c r="B16" t="n">
-        <v>6079</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>12698</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2579,16 +2296,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>101463</v>
+        <v>100713</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tvåfärgad barksvartbagge</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Opilo mollis</t>
+          <t>Corticeus bicolor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Olivier, 1790)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2619,10 +2341,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603068.0020412052</v>
+        <v>603044</v>
       </c>
       <c r="R16" t="n">
-        <v>6304920.253093851</v>
+        <v>6304886</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2652,24 +2374,14 @@
           <t>2021-06-14</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-07-15</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>trädfönster B2, på vad ser ut som en död ask</t>
+          <t>trädfönster B1, på vad ser ut som en död ask</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2685,11 +2397,6 @@
       <c r="AI16" t="inlineStr">
         <is>
           <t>ädellövskog</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>Roger Mugerwa Pettersson</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2707,42 +2414,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>97488052</v>
+        <v>97488103</v>
       </c>
       <c r="B17" t="n">
-        <v>9299</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>10677</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100859</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Bokoxe</t>
-        </is>
+        <v>100782</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dorcus parallelipipedus</t>
+          <t>Cypha apicalis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brisout de Barneville, 1863)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2768,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603068.0020412052</v>
+        <v>603156</v>
       </c>
       <c r="R17" t="n">
-        <v>6304920.253093851</v>
+        <v>6304901</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2801,24 +2498,14 @@
           <t>2021-06-14</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-07-15</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>trädfönster B2, på vad ser ut som en död ask</t>
+          <t>trädfönster B4, på vad ser ut som en död ask</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2834,6 +2521,11 @@
       <c r="AI17" t="inlineStr">
         <is>
           <t>ädellövskog</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>Roger Mugerwa Pettersson</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2851,15 +2543,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>97498652</v>
+        <v>97488052</v>
       </c>
       <c r="B18" t="n">
-        <v>96361</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9403</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2867,45 +2554,58 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219864</v>
+        <v>100859</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Bokoxe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Dorcus parallelipipedus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kolstad 39:33, Öl</t>
+          <t>Furuhäll, Öl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603177.3517046175</v>
+        <v>603068</v>
       </c>
       <c r="R18" t="n">
-        <v>6304795.586559884</v>
+        <v>6304920</v>
       </c>
       <c r="S18" t="n">
-        <v>123</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2929,27 +2629,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rapporterad i efterhand, tidpunkt osäker</t>
+          <t>trädfönster B2, på vad ser ut som en död ask</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2962,30 +2652,30 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>ädellövskog</t>
+        </is>
+      </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Tingnert</t>
+          <t>Roger Mugerwa Pettersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Tingnert</t>
+          <t>Ruaridh Hägglund</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>97498911</v>
+        <v>109895709</v>
       </c>
       <c r="B19" t="n">
-        <v>57549</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9406</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2993,16 +2683,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>208245</v>
+        <v>101246</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3012,24 +2702,32 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kolstad 39:33, Öl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>603177.3517046175</v>
+        <v>603177</v>
       </c>
       <c r="R19" t="n">
-        <v>6304795.586559884</v>
+        <v>6304796</v>
       </c>
       <c r="S19" t="n">
         <v>123</v>
@@ -3056,27 +2754,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rapporterad i efterhand, tidpunkt osäker.</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3104,62 +2797,69 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>97498730</v>
+        <v>97488069</v>
       </c>
       <c r="B20" t="n">
-        <v>57576</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>7170</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100117</v>
+        <v>101784</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Entandad plattbagge</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rana dalmatina</t>
+          <t>Silvanus unidentatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Bonaparte, 1840</t>
+          <t>(Olivier, 1790)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kolstad 39:33, Öl</t>
+          <t>Furuhäll, Öl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>603177.3517046175</v>
+        <v>603068</v>
       </c>
       <c r="R20" t="n">
-        <v>6304795.586559884</v>
+        <v>6304920</v>
       </c>
       <c r="S20" t="n">
-        <v>123</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3183,27 +2883,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rapporterad i efterhand, tidpunkt osäker.</t>
+          <t>trädfönster B2, på vad ser ut som en död ask</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3216,30 +2906,35 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>ädellövskog</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>Roger Mugerwa Pettersson</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Tingnert</t>
+          <t>Roger Mugerwa Pettersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Tingnert</t>
+          <t>Ruaridh Hägglund</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>97488076</v>
+        <v>97488044</v>
       </c>
       <c r="B21" t="n">
-        <v>12472</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4760</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3247,21 +2942,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102289</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Vasstandad trädbasbagge</t>
-        </is>
+        <v>101929</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lissodema denticolle</t>
+          <t>Trinodes hirtus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1813)</t>
+          <t>(Fabricius, 1781)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3292,10 +2982,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603035.9007419299</v>
+        <v>603034</v>
       </c>
       <c r="R21" t="n">
-        <v>6304933.672362258</v>
+        <v>6304778</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3325,24 +3015,14 @@
           <t>2021-06-14</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2021-07-15</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>trädfönster B3, på björk</t>
+          <t>trädfönster A2, på vad ser ut som en död ask</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3375,15 +3055,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>97487718</v>
+        <v>97488047</v>
       </c>
       <c r="B22" t="n">
-        <v>5104</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4760</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3391,21 +3066,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100276</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Prydnadsbock</t>
-        </is>
+        <v>101929</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Anaglyptus mysticus</t>
+          <t>Trinodes hirtus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1781)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3436,10 +3106,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603068.0020412052</v>
+        <v>603156</v>
       </c>
       <c r="R22" t="n">
-        <v>6304920.253093851</v>
+        <v>6304901</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3469,24 +3139,14 @@
           <t>2021-06-14</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2021-07-15</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>trädfönster B2, på vad ser ut som en död ask</t>
+          <t>trädfönster B4, på vad ser ut som en död ask</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3519,74 +3179,56 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>97488058</v>
+        <v>97498898</v>
       </c>
       <c r="B23" t="n">
-        <v>8294</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106540</v>
+        <v>102977</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Furuhäll, Öl</t>
+          <t>Kolstad 39:33, Öl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>603068.0020412052</v>
+        <v>603177</v>
       </c>
       <c r="R23" t="n">
-        <v>6304920.253093851</v>
+        <v>6304796</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3610,27 +3252,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-06-14</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>trädfönster B2, på vad ser ut som en död ask</t>
+          <t>Rapporterad i efterhand, tidpunkt osäker.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3639,61 +3271,50 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>ädellövskog</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Roger Mugerwa Pettersson</t>
+          <t>Jan Tingnert</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Jan Tingnert</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>109895709</v>
+        <v>97488057</v>
       </c>
       <c r="B24" t="n">
-        <v>9302</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8369</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>101246</v>
+        <v>106540</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3706,27 +3327,31 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fönsterfälla</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kolstad 39:33, Öl</t>
+          <t>Furuhäll, Öl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>603177.3517046175</v>
+        <v>603156</v>
       </c>
       <c r="R24" t="n">
-        <v>6304795.586559884</v>
+        <v>6304901</v>
       </c>
       <c r="S24" t="n">
-        <v>123</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3750,22 +3375,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2021-06-14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2021-07-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>trädfönster B4, på vad det ser ut som en död ask</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3778,75 +3398,89 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>ädellövskog</t>
+        </is>
+      </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jan Tingnert</t>
+          <t>Roger Mugerwa Pettersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Tingnert</t>
+          <t>Ruaridh Hägglund</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>99826221</v>
+        <v>97488058</v>
       </c>
       <c r="B25" t="n">
-        <v>103300</v>
+        <v>8369</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1661</v>
+        <v>106540</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Silverviol</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Viola alba</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Besser</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Furuhäll 2, Öl</t>
+          <t>Furuhäll, Öl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>602996</v>
+        <v>603068</v>
       </c>
       <c r="R25" t="n">
-        <v>6304889</v>
+        <v>6304920</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3868,24 +3502,19 @@
           <t>Köping</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>Hö-Bor-5755</t>
-        </is>
-      </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-04-11</t>
+          <t>2021-06-14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-04-11</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>i kanten av hagtornshäck mot väg</t>
+          <t>trädfönster B2, på vad ser ut som en död ask</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3898,79 +3527,77 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>ädellövskog</t>
+        </is>
+      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kornelia Samarzija</t>
+          <t>Roger Mugerwa Pettersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kornelia Samarzija</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>99826149</v>
+        <v>97498911</v>
       </c>
       <c r="B26" t="n">
-        <v>103300</v>
+        <v>58790</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1661</v>
+        <v>208245</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Silverviol</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Viola alba</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Besser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Furuhäll (1), Öl</t>
+          <t>Kolstad 39:33, Öl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>602979</v>
+        <v>603177</v>
       </c>
       <c r="R26" t="n">
-        <v>6304852</v>
+        <v>6304796</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3992,24 +3619,19 @@
           <t>Köping</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>Hö-Bor-0083</t>
-        </is>
-      </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-04-11</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-04-11</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Östra Bergklintsvägen 18 på stugtomt vid huset och kanten av buskage över till fastighet nr 20</t>
+          <t>Rapporterad i efterhand, tidpunkt osäker.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4025,89 +3647,69 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kornelia Samarzija</t>
+          <t>Jan Tingnert</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kornelia Samarzija</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Jan Tingnert</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>106536624</v>
+        <v>97498902</v>
       </c>
       <c r="B27" t="n">
-        <v>101105</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56905</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1661</v>
+        <v>208260</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Silverviol</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Viola alba</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Besser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Häck, Borgholm, Öl</t>
+          <t>Kolstad 39:33, Öl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>603010.4545132001</v>
+        <v>603177</v>
       </c>
       <c r="R27" t="n">
-        <v>6304877.284820545</v>
+        <v>6304796</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4131,27 +3733,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-04-08</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-04-08</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>WSP Sverige AB</t>
+          <t>Rapporterad i efterhand, tidpunkt osäker.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4167,69 +3759,68 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Simon Selberg</t>
+          <t>Jan Tingnert</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Simon Selberg</t>
+          <t>Jan Tingnert</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>108157184</v>
+        <v>97498698</v>
       </c>
       <c r="B28" t="n">
-        <v>101105</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1661</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Silverviol</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Viola alba</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Besser</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Furuhäll 3, Öl</t>
+          <t>Kolstad 39:33, Öl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>603138.8624946685</v>
+        <v>603177</v>
       </c>
       <c r="R28" t="n">
-        <v>6304735.046768321</v>
+        <v>6304796</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4251,33 +3842,23 @@
           <t>Köping</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>Hö-Bor-5756</t>
-        </is>
-      </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-04-15</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-04-15</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-31</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rapporterad i efterhand, tidpunkt osäker.</t>
         </is>
       </c>
       <c r="AD28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
@@ -4289,83 +3870,68 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kornelia Samarzija</t>
+          <t>Jan Tingnert</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kornelia Samarzija</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Jan Tingnert</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>6768133</v>
+        <v>97498652</v>
       </c>
       <c r="B29" t="n">
-        <v>101105</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1661</v>
+        <v>219864</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Silverviol</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Viola alba</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Besser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Furuhäll, Öl</t>
+          <t>Kolstad 39:33, Öl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>602974.4056083336</v>
+        <v>603177</v>
       </c>
       <c r="R29" t="n">
-        <v>6304873.11416917</v>
+        <v>6304796</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4389,22 +3955,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2008-04-05</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2008-04-05</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rapporterad i efterhand, tidpunkt osäker</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4413,85 +3974,75 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Jan Tingnert</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Eva Bjelkendal, Ulla-Britt Andersson</t>
+          <t>Jan Tingnert</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>6768135</v>
+        <v>97498679</v>
       </c>
       <c r="B30" t="n">
-        <v>101105</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1661</v>
+        <v>221141</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Silverviol</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Viola alba</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Besser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Furuhäll, Öl</t>
+          <t>Kolstad 39:33, Öl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>602993.2204704867</v>
+        <v>603177</v>
       </c>
       <c r="R30" t="n">
-        <v>6304865.379152378</v>
+        <v>6304796</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4515,22 +4066,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2008-04-05</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2008-04-05</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rapporterad i efterhand, tidpunkt osäker.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4539,79 +4085,75 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Jan Tingnert</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Eva Bjelkendal, Ulla-Britt Andersson</t>
+          <t>Jan Tingnert</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>97498807</v>
+        <v>95668703</v>
       </c>
       <c r="B31" t="n">
-        <v>101105</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106386</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1661</v>
+        <v>224190</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Silverviol</t>
+          <t>Flockarun</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Viola alba</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Besser</t>
-        </is>
-      </c>
+          <t>Centaurium erythraea var. erythraea</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kolstad 39:33, Öl</t>
+          <t>Furuhäll 4, Öl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>603177.3517046175</v>
+        <v>603011</v>
       </c>
       <c r="R31" t="n">
-        <v>6304795.586559884</v>
+        <v>6304960</v>
       </c>
       <c r="S31" t="n">
-        <v>123</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4633,29 +4175,19 @@
           <t>Köping</t>
         </is>
       </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Hö-Bor-5757</t>
+        </is>
+      </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2021-04-30</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rapporterad i efterhand, tidpunkt osäker.</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4668,151 +4200,25 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>gammalt stenbrott</t>
+        </is>
+      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jan Tingnert</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jan Tingnert</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>119959940</v>
-      </c>
-      <c r="B32" t="n">
-        <v>56243</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>100053</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Igelkott</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Erinaceus europaeus</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Predikstolen, Öl</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>603052</v>
-      </c>
-      <c r="R32" t="n">
-        <v>6304833</v>
-      </c>
-      <c r="S32" t="n">
-        <v>50</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Borgholm</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Öland</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Köping</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Johan Nilsson</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Via Johan Nilsson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+          <t>Thomas Gunnarsson, Sten Linder-Aronson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 43587-2021 artfynd.xlsx
+++ b/artfynd/A 43587-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6768133</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6768138</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6768135</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95668336</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95668346</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1358,6 +1388,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97498807</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1481,6 +1516,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106536624</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1594,6 +1634,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/559779</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1706,6 +1751,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97498759</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1816,6 +1866,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97498886</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1944,6 +1999,11 @@
       <c r="AY12" t="inlineStr">
         <is>
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119959940</t>
         </is>
       </c>
     </row>
@@ -2058,6 +2118,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97498905</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2170,6 +2235,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97498730</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2282,6 +2352,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97498949</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2411,6 +2486,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97488071</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2540,6 +2620,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97488103</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2669,6 +2754,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97488052</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2794,6 +2884,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109895709</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2928,6 +3023,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97488069</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3052,6 +3152,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97488044</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3176,6 +3281,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97488047</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3286,6 +3396,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97498898</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3415,6 +3530,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97488057</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3544,6 +3664,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97488058</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3656,6 +3781,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97498911</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3768,6 +3898,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97498902</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3879,6 +4014,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97498698</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3990,6 +4130,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97498652</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4101,6 +4246,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97498679</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4221,8 +4371,45 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95668703</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>